--- a/Configs/GameConfig/Datas/fg/#WorldGenVersion-生成器版本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#WorldGenVersion-生成器版本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:BI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,171 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>startClearSet</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>settingSet</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>guaranteeSet</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>startFlatRadius</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>startFlatPollution</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>startNoOutpostRadius</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>startStampAttempts</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>riverCount</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>riverStartDistance</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>riverSegments</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>riverSegmentLength</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>riverTurnMax</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>riverHalfWidth</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>riverHalfWidthMax</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>riverFordPeriod</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>riverFordWidth</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>beltCount</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>beltRareEvery</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>beltMinDistance</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>beltMaxDistance</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>beltLength</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>beltRadius</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>beltOreBonus</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>poiCellSize</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>relicChance</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>nestChance</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>nestTierDistance</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>nestMaxTier</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>poiEdgeMargin</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>poiShiftRadius</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>riverOutwardMaxAngle</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>riverWidenTotal</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>relicCoreExclusion</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -699,6 +864,171 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -833,10 +1163,175 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>本版本使用的世界设置集合(fg.TbWorldPreset 的 set);已发布集合禁止改</t>
+          <t>本版本使用的世界设置预设集合(fg.TbWorldPreset 的 set);v2 起世界设置改为分项(settingSet),填 none</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
+        <is>
+          <t>起始区平地快照集合(fg.TbWorldStartClear 的 set):开局布局占地+外圈的矩形,相对核心;已发布集合禁止改</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>分项世界设置集合(fg.TbWorldSettingAxis 的 set);none=用 presetSet 的整套预设(v1)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>起始区资源保证集合(fg.TbWorldStartGuarantee 的 set);none=没有保证(v1)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>起始区第1级:核心半径内没有悬崖、污染&lt;=startFlatPollution(格,欧氏);0=不启用</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>起始区第1级的污染上限(0~3)</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>起始区第3级:核心半径内没有敌方建筑(格);据点生成避开</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>某项保证不满足时,派生子种子确定性重试放置的次数上限(之后逐个候选兜底)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>规划层主要河流条数(FGR-GEN-020)</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>河流起点离核心的距离(格),向外流</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>每条河的折线段数</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>每段长度(格)</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>每段方向最大偏转(度);方向与离心方向的夹角不超过 75 度(不回流进家园)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>河道半宽起始值(格),沿河逐段加宽</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>河道半宽上限(格)</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>每隔多少格有一处浅滩(可通行,保证领地可达)</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>浅滩宽度(格)</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>规划层矿带条数(FGR-GEN-020)</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>每几条矿带有一条是稀土矿带(其余金属)</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>矿带起点离核心最近(格)</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>矿带起点离核心最远(格)</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>矿带长度(格)</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>矿带半宽(格)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>矿带内矿阈值下降量(越大矿越密)</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>遗迹点/据点的分布格边长(格);每个分布格按(种子,格坐标)独立决定,与访问顺序无关</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>每个分布格出现遗迹点的概率(0~1)</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>家园区每个分布格出现侦察巢的概率(0~1,再乘世界设置“据点密度”)</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>侦察巢离核心每远这么多格强一级(FGR-GEN-032)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>侦察巢最高等级</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>点位离分布格边缘至少多少格</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>点位落在悬崖/水面上时就近挪位的最大半径(格);挪不动就不生成</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>河流每段方向与离心方向的最大夹角(度);&lt;=90,河不会流回家园</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>河道沿河总共加宽多少格(逐段线性,再受 riverHalfWidthMax 限制)</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>遗迹点离核心至少多少格(格,欧氏);起始区里不放遗迹点</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
         <is>
           <t>这一版改了什么</t>
         </is>
@@ -928,7 +1423,307 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>FG0-ARCH-05 首版：定点噪声、距离污染与资源、领地污染与危害带、室内表面</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>150</v>
+      </c>
+      <c r="L5" t="n">
+        <v>600</v>
+      </c>
+      <c r="M5" t="n">
+        <v>500</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>200</v>
+      </c>
+      <c r="X5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>FG3-GEN-01：起始区四级保证与局部重生成、河流与矿带、分项世界设置、遗迹点与侦察巢分布</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#WorldGenVersion-生成器版本.xlsx
+++ b/Configs/GameConfig/Datas/fg/#WorldGenVersion-生成器版本.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,6 +719,46 @@
       </c>
       <c r="BI1" t="inlineStr">
         <is>
+          <t>templateSet</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>anchorSet</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>scatterOutpostChance</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>scatterTierDistance</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>outpostMaxTier</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>outerZoneDistance</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>outerOutpostChance</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>outerCacheChance</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1029,6 +1069,46 @@
           <t>string</t>
         </is>
       </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1332,6 +1412,46 @@
         </is>
       </c>
       <c r="BI3" t="inlineStr">
+        <is>
+          <t>领地模板集合(fg.TbTerritoryTemplate 的 set);none=没有领地模板(v1/v2)</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>手工锚点集合(fg.TbAnchorSite 的 set);none=没有手工锚点(v1/v2)</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>领地之间(家园区外、外延区内、不在领地里)每个分布格出现零散前哨的概率(再乘据点密度)</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>零散前哨离核心每远这么多格强一级(FGR-GEN-032)</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>零散前哨 / 外延区前哨的最高等级</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>外延区起点离核心的距离(格,FGR-GEN-040 初值 2500)</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>外延区每个分布格出现零散前哨的概率(再乘据点密度;越远越强)</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>外延区每个分布格出现资源缓存的概率(越远奖励越高)</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>这一版改了什么</t>
         </is>
@@ -1528,6 +1648,34 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
           <t>FG0-ARCH-05 首版：定点噪声、距离污染与资源、领地污染与危害带、室内表面</t>
         </is>
       </c>
@@ -1723,7 +1871,258 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
           <t>FG3-GEN-01：起始区四级保证与局部重生成、河流与矿带、分项世界设置、遗迹点与侦察巢分布</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>150</v>
+      </c>
+      <c r="L6" t="n">
+        <v>600</v>
+      </c>
+      <c r="M6" t="n">
+        <v>500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>200</v>
+      </c>
+      <c r="X6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>64</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>tt3</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>as3</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>400</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>FG8-GEN-02：阵营领地模板、手工锚点与室内入口、领地之间与外延区的零散前哨和缓存</t>
         </is>
       </c>
     </row>
